--- a/output/pdf_financials_xlsx/RM.xlsx
+++ b/output/pdf_financials_xlsx/RM.xlsx
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.760511</v>
+        <v>20.221329</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.760511</v>
+        <v>8.993786</v>
       </c>
     </row>
     <row r="93">
@@ -2730,7 +2730,11 @@
           <t>Reserves (Notes 17, 18, 19 and 20)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>19.460818</v>
       </c>

--- a/output/pdf_financials_xlsx/RM.xlsx
+++ b/output/pdf_financials_xlsx/RM.xlsx
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.015419</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.0103</v>
       </c>
     </row>
     <row r="102">
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.882745</v>
       </c>
     </row>
     <row r="111">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.191807</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.032233</v>
       </c>
     </row>
     <row r="112">
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.740607</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>1.173074</v>
       </c>
     </row>
     <row r="116">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.191807</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.032233</v>
       </c>
     </row>
     <row r="135">
@@ -3032,7 +3032,11 @@
           <t>Accretion expense (Note 13)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3164,7 +3168,11 @@
           <t>Write off of GST receivable</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -3320,7 +3328,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>-0.015419</v>
       </c>
@@ -3530,7 +3542,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>-0.191807</v>
       </c>
@@ -3684,7 +3700,11 @@
           <t>Proceeds from sale of equity investments (Note 11, 25)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.740607</v>
       </c>
